--- a/data/trans_camb/IP16B05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Clase-trans_camb.xlsx
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,92</t>
+          <t>0,0; 49,67</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,92</t>
+          <t>0,0; 49,64</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,17</t>
+          <t>0,0; 24,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,57</t>
+          <t>0,0; 29,8</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 99,7</t>
+          <t>0,0; 98,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 99,7</t>
+          <t>0,0; 98,55</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,2</t>
+          <t>0,0; 32,47</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,98</t>
+          <t>0,0; 42,45</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 0,0</t>
+          <t>-38,38; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,48; 0,0</t>
+          <t>-38,38; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,92</t>
+          <t>0,0; 26,81</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,33</t>
+          <t>0,0; 26,75</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 0,0</t>
+          <t>-17,64; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 10,66</t>
+          <t>-3,02; 10,64</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,88</t>
+          <t>0,0; 36,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,61</t>
+          <t>0,0; 36,53</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 0,0</t>
+          <t>-17,64; 0,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,01; 11,91</t>
+          <t>-3,03; 11,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,11</t>
+          <t>0,0; 15,1</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B05-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP16B05-Clase-trans_camb.xlsx
@@ -1099,12 +1099,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,67</t>
+          <t>0,0; 49,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,64</t>
+          <t>0,0; 49,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,51</t>
+          <t>0,0; 29,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,8</t>
+          <t>0,0; 29,5</t>
         </is>
       </c>
     </row>
@@ -1175,12 +1175,12 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 98,68</t>
+          <t>0,0; 98,52</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 98,55</t>
+          <t>0,0; 98,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1195,12 +1195,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,47</t>
+          <t>0,0; 41,14</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,45</t>
+          <t>0,0; 41,83</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 0,0</t>
+          <t>-39,2; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-38,38; 0,0</t>
+          <t>-39,2; 0,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,81</t>
+          <t>0,0; 27,83</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,75</t>
+          <t>0,0; 33,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 0,0</t>
+          <t>-17,94; 0,0</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-3,02; 10,64</t>
+          <t>-3,04; 10,63</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,12</t>
+          <t>0,0; 12,6</t>
         </is>
       </c>
     </row>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,63</t>
+          <t>0,0; 38,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,53</t>
+          <t>0,0; 50,86</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-17,64; 0,0</t>
+          <t>-17,94; 0,0</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -1663,12 +1663,12 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 11,9</t>
+          <t>-3,05; 11,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,1</t>
+          <t>0,0; 14,51</t>
         </is>
       </c>
     </row>
